--- a/out/MLP_Base_repeat_5_000007.xlsx
+++ b/out/MLP_Base_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.544994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5730533708028094</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.544994382064366</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.544994382064366</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.544994382064366</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.000294076475623995</v>
+        <v>-0.0002304963295231573</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.390267440835934</v>
+        <v>2.657282258148526</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.544994382064366</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.785775623298086</v>
+        <v>5.318672195111753</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.5083857259756837</v>
+        <v>0.3984713281492763</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.544994382064366</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.407729429176656</v>
+        <v>3.454766154962189</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6356475187464935</v>
+        <v>0.4982188143719568</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.544994382064366</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.170719589469075</v>
+        <v>4.052795735582627</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9111978663021727</v>
+        <v>0.7141943076484688</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.544994382064366</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.357826413938764</v>
+        <v>4.983246703436129</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9748008790059393</v>
+        <v>0.7640464417289148</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.544994382064366</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.396298939575981</v>
+        <v>5.797198528289283</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.033093189275808</v>
+        <v>0.8097344897931371</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.544994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.487757506227002</v>
+        <v>6.652680358144429</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4662157420527285</v>
+        <v>0.3654187810370038</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.944994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.38623730472084</v>
+        <v>6.57310906756193</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2251608943023893</v>
+        <v>0.1764799260497761</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.944994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.369977774425758</v>
+        <v>6.56036488766905</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1072824626685446</v>
+        <v>0.08408804351640738</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.944994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.359202996494439</v>
+        <v>6.551919611777429</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03178668214998914</v>
+        <v>0.02491433754713157</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.944994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.315380348975356</v>
+        <v>6.51757140064352</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02102570490037912</v>
+        <v>0.01648038569659515</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.944994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.325628714414307</v>
+        <v>6.525604098924183</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01075946898473934</v>
+        <v>0.008432415132005471</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.32610805826077</v>
+        <v>6.525978719905607</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005501441891907545</v>
+        <v>0.004310560583292075</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.944994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.3263450923232</v>
+        <v>6.526163414040948</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002065080248495467</v>
+        <v>0.001617761262440323</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.944994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.324969389133802</v>
+        <v>6.525084099060212</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001123608176889768</v>
+        <v>0.0008794064076212218</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.325149614748652</v>
+        <v>6.525224246618048</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005385952861818967</v>
+        <v>0.000420975253499264</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.325102483499061</v>
+        <v>6.525186231486789</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003315126501627838</v>
+        <v>0.0002586999714725908</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.325226659322402</v>
+        <v>6.525282456985783</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001710221259300122</v>
+        <v>0.0001329354671030505</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.325236995407543</v>
+        <v>6.525289474736714</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.99229161167401e-05</v>
+        <v>6.193923976260691e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.944994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.325226708616551</v>
+        <v>6.525280331394765</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.00032942437966e-05</v>
+        <v>3.721183046616949e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.544994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.32524575537068</v>
+        <v>6.525294066270207</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.947783683037037e-05</v>
+        <v>1.481539171982363e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5730533708028094</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.325235837756075</v>
+        <v>6.525285177363889</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>3.234953259883613e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.325227823050861</v>
+        <v>6.525277848445199</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.325223733238371</v>
+        <v>6.525273593267028</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.544994382064366</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.325217865795686</v>
+        <v>6.525267870987998</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>2.544994382064366</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.325212796440319</v>
+        <v>6.525262801632628</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.544994382064366</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.325208431466351</v>
+        <v>6.52525843665866</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.544994382064366</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.325209522712806</v>
+        <v>6.525259527905117</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.544994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.32520883310567</v>
+        <v>6.525258838297981</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>2.544994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.325208863418073</v>
+        <v>6.525258868610383</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.544994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.325208673965562</v>
+        <v>6.525258679157873</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.544994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.325208727012265</v>
+        <v>6.525258732204576</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.325208780058967</v>
+        <v>6.525258785251278</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.325208742168465</v>
+        <v>6.525258747360776</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.325208613340759</v>
+        <v>6.525258618533069</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.325208469356852</v>
+        <v>6.525258474549163</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.325208310216743</v>
+        <v>6.525258315409054</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.325208363263448</v>
+        <v>6.525258368455757</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.325208310216743</v>
+        <v>6.525258315409054</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.325208310216743</v>
+        <v>6.525258315409054</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.544994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.325208128342334</v>
+        <v>6.525258133534645</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.544994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.325208295060543</v>
+        <v>6.525258300252853</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.325208492091154</v>
+        <v>6.525258497283463</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.325208332951044</v>
+        <v>6.525258338143355</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.325208370841546</v>
+        <v>6.525258376033856</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.544994382064366</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.325208567872158</v>
+        <v>6.525258573064467</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5730533708028094</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.325208545137857</v>
+        <v>6.525258550330165</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.325208393575847</v>
+        <v>6.525258398768158</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.325208317794845</v>
+        <v>6.525258322987154</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.325208416310149</v>
+        <v>6.52525842150246</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.544994382064366</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.325208423888249</v>
+        <v>6.52525842908056</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5730533708028094</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.325208689121762</v>
+        <v>6.525258694314074</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5730533708028094</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.325208393575847</v>
+        <v>6.525258398768158</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.544994382064366</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.325208636075061</v>
+        <v>6.525258641267371</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.325208719434164</v>
+        <v>6.525258724626475</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.544994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.325208552715955</v>
+        <v>6.525258557908267</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>2.544994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.325208742168465</v>
+        <v>6.525258747360776</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5730533708028094</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.325208393575847</v>
+        <v>6.525258398768158</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.325208188967137</v>
+        <v>6.525258194159448</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.325208302638643</v>
+        <v>6.525258307830953</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.325208317794845</v>
+        <v>6.525258322987154</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.325208082873733</v>
+        <v>6.525258088066042</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.325208143498534</v>
+        <v>6.525258148690845</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.325208014670828</v>
+        <v>6.525258019863138</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.544994382064366</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.325208151076636</v>
+        <v>6.525258156268946</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5730533708028094</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.325208325372945</v>
+        <v>6.525258330565254</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.325208469356852</v>
+        <v>6.525258474549163</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.325208302638643</v>
+        <v>6.525258307830953</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.325208295060543</v>
+        <v>6.525258300252853</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.325208007092728</v>
+        <v>6.525258012285038</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.325208022248928</v>
+        <v>6.525258027441239</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.325208249591942</v>
+        <v>6.525258254784251</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.111245132341913</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.325208234435738</v>
+        <v>6.52525823962805</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.325208340529146</v>
+        <v>6.525258345721455</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.325208067717529</v>
+        <v>6.525258072909842</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.325208166232835</v>
+        <v>6.525258171425146</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.325208317794845</v>
+        <v>6.525258322987154</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.325208332951044</v>
+        <v>6.525258338143355</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.325208310216743</v>
+        <v>6.525258315409054</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.325208393575847</v>
+        <v>6.525258398768158</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.325208492091154</v>
+        <v>6.525258497283463</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.088844415955533</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.325208325372945</v>
+        <v>6.525258330565254</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.325208310216743</v>
+        <v>6.525258315409054</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.325208279904341</v>
+        <v>6.525258285096652</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.325208264748142</v>
+        <v>6.525258269940451</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.325208302638643</v>
+        <v>6.525258307830953</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.173053370802809</v>
+        <v>-1.688844415955533</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.325208317794845</v>
+        <v>6.525258322987154</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.173053370802809</v>
+        <v>1.711245132341913</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.325208310216743</v>
+        <v>6.525258315409054</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_5_000007.xlsx
+++ b/out/MLP_Base_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628527</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.544994382064366</v>
+        <v>0.07403146067628522</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.2740314606762853</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.2740314606762853</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.000294076475623995</v>
+        <v>-0.0002295949253633153</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.390267440835934</v>
+        <v>2.646890399473498</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.785775623298086</v>
+        <v>5.29787241382359</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.5083857259756837</v>
+        <v>0.3969129998948502</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.407729429176656</v>
+        <v>3.441255568568601</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6356475187464935</v>
+        <v>0.4962704537473566</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.170719589469075</v>
+        <v>4.036946463347366</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9111978663021727</v>
+        <v>0.7114011792580922</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.357826413938764</v>
+        <v>4.963758761102659</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9748008790059393</v>
+        <v>0.7610586956733684</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.396298939575981</v>
+        <v>5.774527688658881</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.033093189275808</v>
+        <v>0.8065680811823666</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.487757506227002</v>
+        <v>6.626664221265318</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4662157420527285</v>
+        <v>0.3639898397222834</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.944994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.38623730472084</v>
+        <v>6.547404087937125</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2251608943023893</v>
+        <v>0.1757904558692132</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129851</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.369977774425758</v>
+        <v>6.534709742182071</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1072824626685446</v>
+        <v>0.08375830571110535</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129851</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.359202996494439</v>
+        <v>6.526297522463484</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03178668214998914</v>
+        <v>0.02481700172884778</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129851</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.315380348975356</v>
+        <v>6.492083501634576</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02102570490037912</v>
+        <v>0.01641600124805221</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.944994382064366</v>
+        <v>0.7867280899030684</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.325628714414307</v>
+        <v>6.500084818093918</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01075946898473934</v>
+        <v>0.008398960658012678</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.7867280899030684</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.32610805826077</v>
+        <v>6.500457956606919</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005501441891907545</v>
+        <v>0.004294453989092711</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.944994382064366</v>
+        <v>0.7867280899030684</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.3263450923232</v>
+        <v>6.500641920113763</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002065080248495467</v>
+        <v>0.001610949298185676</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.944994382064366</v>
+        <v>0.7867280899030684</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.324969389133802</v>
+        <v>6.499566864773452</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001123608176889768</v>
+        <v>0.0008761063837121873</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628533</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.325149614748652</v>
+        <v>6.49970647073592</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005385952861818967</v>
+        <v>0.0004193857935981474</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.325102483499061</v>
+        <v>6.49966857879545</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003315126501627838</v>
+        <v>0.0002577160163551558</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.325226659322402</v>
+        <v>6.499764426587357</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001710221259300122</v>
+        <v>0.0001319060979455651</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628533</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.325236995407543</v>
+        <v>6.499771400122182</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.99229161167401e-05</v>
+        <v>6.193923976260691e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.944994382064366</v>
+        <v>0.7867280899030684</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.325226708616551</v>
+        <v>6.499762256780234</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.00032942437966e-05</v>
+        <v>3.721183046616949e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.32524575537068</v>
+        <v>6.499775991655675</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.947783683037037e-05</v>
+        <v>1.481539171982363e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.2740314606762854</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.325235837756075</v>
+        <v>6.499767102749358</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>3.234953259883613e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.325227823050861</v>
+        <v>6.499759773830667</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.0740314606762854</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.325223733238371</v>
+        <v>6.499755518652496</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.325217865795686</v>
+        <v>6.499749796373466</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.325212796440319</v>
+        <v>6.499744727018097</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.325208431466351</v>
+        <v>6.499740362044129</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.325209522712806</v>
+        <v>6.499741453290586</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.32520883310567</v>
+        <v>6.49974076368345</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.325208863418073</v>
+        <v>6.499740793995851</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129851</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.325208673965562</v>
+        <v>6.499740604543342</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.325208727012265</v>
+        <v>6.499740657590045</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.0740314606762854</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.325208780058967</v>
+        <v>6.499740710636747</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.325208742168465</v>
+        <v>6.499740672746245</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.325208613340759</v>
+        <v>6.499740543918538</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.325208469356852</v>
+        <v>6.499740399934631</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.325208310216743</v>
+        <v>6.499740240794523</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.325208363263448</v>
+        <v>6.499740293841225</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.325208310216743</v>
+        <v>6.499740240794523</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.0740314606762854</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.325208310216743</v>
+        <v>6.499740240794523</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.325208128342334</v>
+        <v>6.499740058920113</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.325208295060543</v>
+        <v>6.499740225638321</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.2740314606762855</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.325208492091154</v>
+        <v>6.499740422668932</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.4386651685504979</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.325208332951044</v>
+        <v>6.499740263528824</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628553</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.325208370841546</v>
+        <v>6.499740301419325</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.544994382064366</v>
+        <v>0.07403146067628551</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.325208567872158</v>
+        <v>6.499740498449936</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.2740314606762855</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.325208545137857</v>
+        <v>6.499740475715634</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.325208393575847</v>
+        <v>6.499740324153627</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.325208317794845</v>
+        <v>6.499740248372623</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628553</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.325208416310149</v>
+        <v>6.499740346887928</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.544994382064366</v>
+        <v>0.07403146067628553</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.325208423888249</v>
+        <v>6.499740354466028</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.2740314606762856</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.325208689121762</v>
+        <v>6.499740619699542</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.2740314606762856</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.325208393575847</v>
+        <v>6.499740324153627</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.544994382064366</v>
+        <v>0.2740314606762856</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.325208636075061</v>
+        <v>6.499740566652839</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.9867280899030687</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.325208719434164</v>
+        <v>6.499740650011944</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030687</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.325208552715955</v>
+        <v>6.499740483293736</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030687</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.325208742168465</v>
+        <v>6.499740672746245</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.2740314606762856</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.325208393575847</v>
+        <v>6.499740324153627</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.325208188967137</v>
+        <v>6.499740119544916</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.325208302638643</v>
+        <v>6.499740233216421</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.325208317794845</v>
+        <v>6.499740248372623</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.325208082873733</v>
+        <v>6.499740013451511</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.325208143498534</v>
+        <v>6.499740074076313</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.07403146067628569</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.325208014670828</v>
+        <v>6.499739945248606</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.544994382064366</v>
+        <v>0.07403146067628565</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.325208151076636</v>
+        <v>6.499740081654415</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5730533708028094</v>
+        <v>0.2740314606762857</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.325208325372945</v>
+        <v>6.499740255950723</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5730533708028094</v>
+        <v>-0.4386651685504979</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.325208469356852</v>
+        <v>6.499740399934631</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4386651685504979</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.325208302638643</v>
+        <v>6.499740233216421</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.325208295060543</v>
+        <v>6.499740225638321</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.325208007092728</v>
+        <v>6.499739937670507</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.325208022248928</v>
+        <v>6.499739952826707</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.325208249591942</v>
+        <v>6.499740180169719</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.325208234435738</v>
+        <v>6.499740165013518</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.325208340529146</v>
+        <v>6.499740271106924</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.325208067717529</v>
+        <v>6.49973999829531</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.325208166232835</v>
+        <v>6.499740096810615</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.325208317794845</v>
+        <v>6.499740248372623</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.325208332951044</v>
+        <v>6.499740263528824</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.325208310216743</v>
+        <v>6.499740240794523</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.325208393575847</v>
+        <v>6.499740324153627</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.325208492091154</v>
+        <v>6.499740422668932</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.325208325372945</v>
+        <v>6.499740255950723</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.325208310216743</v>
+        <v>6.499740240794523</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.325208279904341</v>
+        <v>6.499740210482121</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.325208264748142</v>
+        <v>6.49974019532592</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.325208302638643</v>
+        <v>6.499740233216421</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.325208317794845</v>
+        <v>6.499740248372623</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.325208310216743</v>
+        <v>6.499740240794523</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_5_000007.xlsx
+++ b/out/MLP_Base_repeat_5_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4071080386638641</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-1</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4132784307003021</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.3977004587650299</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.07403146067628527</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5258936285972595</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.07403146067628522</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4692887663841248</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.2740314606762853</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4288299083709717</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3957948088645935</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4085440039634705</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4060351848602295</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4069910943508148</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.395045131444931</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3847890794277191</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4093195497989655</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4029077887535095</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4258163571357727</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4000832140445709</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4023306667804718</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.3866766393184662</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4109509289264679</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.16</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.412548840045929</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4402410387992859</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4975418746471405</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4455326497554779</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4212641716003418</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4075193405151367</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3988017141819</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3852882981300354</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4317668378353119</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4266037344932556</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4118820428848267</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.400045782327652</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3977055847644806</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4069255888462067</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4116057455539703</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4907386004924774</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.2740314606762853</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.6346504688262939</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5622695684432983</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.699424719129851</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5498892664909363</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.699424719129851</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002295949253633153</v>
+        <v>-0.0001762581139509566</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.646890399473498</v>
+        <v>2.031995661651695</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.5406172275543213</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.699424719129851</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>5.29787241382359</v>
+        <v>4.067132573440041</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3969129998948502</v>
+        <v>0.304706836431729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5330641865730286</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.699424719129851</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.441255568568601</v>
+        <v>2.641823215454815</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4962704537473566</v>
+        <v>0.3809826339917982</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5064815282821655</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.699424719129851</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.036946463347366</v>
+        <v>3.099130150153705</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.7114011792580922</v>
+        <v>0.5461367990545677</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.5826584100723267</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.699424719129851</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.963758761102659</v>
+        <v>3.810636331820818</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.7610586956733684</v>
+        <v>0.5842581963286199</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.6241800785064697</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.699424719129851</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.774527688658881</v>
+        <v>4.43305701572845</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.8065680811823666</v>
+        <v>0.619196663161341</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.6689783334732056</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.699424719129851</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>6.626664221265318</v>
+        <v>5.087235660467096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3639898397222834</v>
+        <v>0.2794319377854967</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.7335931062698364</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.699424719129851</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>6.547404087937125</v>
+        <v>5.026388322909726</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1757904558692132</v>
+        <v>0.1349522109205024</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5497979521751404</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.499424719129851</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>6.534709742182071</v>
+        <v>5.016642981444461</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.08375830571110535</v>
+        <v>0.06430132361609035</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.6321461796760559</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.499424719129851</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>6.526297522463484</v>
+        <v>5.010184959644628</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02481700172884778</v>
+        <v>0.01905167046229239</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.5330760478973389</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.499424719129851</v>
+        <v>-0.16</v>
       </c>
       <c r="JC49" t="n">
-        <v>6.492083501634576</v>
+        <v>4.983919210836554</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01641600124805221</v>
+        <v>0.01260080754943257</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.5397341847419739</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.7867280899030684</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>6.500084818093918</v>
+        <v>4.990060604748933</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.008398960658012678</v>
+        <v>0.00644679370502156</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.4773347973823547</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.7867280899030684</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>6.500457956606919</v>
+        <v>4.990345910255853</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.004294453989092711</v>
+        <v>0.003295845148732146</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.5146353244781494</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7867280899030684</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>6.500641920113763</v>
+        <v>4.990485984322567</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001610949298185676</v>
+        <v>0.001235534379262914</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5138983130455017</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.7867280899030684</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>6.499566864773452</v>
+        <v>4.9896594645375</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0008761063837121873</v>
+        <v>0.0006715049013520539</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4877652227878571</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.07403146067628533</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>6.49970647073592</v>
+        <v>4.989765491587336</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0004193857935981474</v>
+        <v>0.0003208392797289147</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.479180783033371</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>6.49966857879545</v>
+        <v>4.98973523747574</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002577160163551558</v>
+        <v>0.0001967107990741833</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4944419860839844</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>6.499764426587357</v>
+        <v>4.989807667428328</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001319060979455651</v>
+        <v>9.999565406351607e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.4109173715114594</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.07403146067628533</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>6.499771400122182</v>
+        <v>4.98981186073719</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.193923976260691e-05</v>
+        <v>4.595374967004406e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.712481677532196</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7867280899030684</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>6.499762256780234</v>
+        <v>4.989803676537635</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.721183046616949e-05</v>
+        <v>2.82578058218305e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.6177356243133545</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>6.499775991655675</v>
+        <v>4.989813216435479</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.481539171982363e-05</v>
+        <v>1.015294660927689e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.4976449608802795</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.2740314606762854</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>6.499767102749358</v>
+        <v>4.989805242565942</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>3.234953259883613e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.4803796112537384</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>6.499759773830667</v>
+        <v>4.989798461775472</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.4938381314277649</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.0740314606762854</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>6.499755518652496</v>
+        <v>4.989794041231621</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.5014452934265137</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.9867280899030685</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>6.499749796373466</v>
+        <v>4.989788462936497</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.5524798631668091</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.699424719129851</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>6.499744727018097</v>
+        <v>4.98978341631543</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.7045787572860718</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.699424719129851</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>6.499740362044129</v>
+        <v>4.989783734595646</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.8783407211303711</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.699424719129851</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>6.499741453290586</v>
+        <v>4.989784825842103</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.7682574987411499</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.699424719129851</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>6.49974076368345</v>
+        <v>4.989784136234967</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.6392170190811157</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.699424719129851</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>6.499740793995851</v>
+        <v>4.989784166547369</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.5761538147926331</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.699424719129851</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>6.499740604543342</v>
+        <v>4.989783977094859</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.5453459620475769</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.16</v>
       </c>
       <c r="JC70" t="n">
-        <v>6.499740657590045</v>
+        <v>4.989784030141562</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.4717177748680115</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.0740314606762854</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>6.499740710636747</v>
+        <v>4.989784083188264</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.4485683143138885</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>6.499740672746245</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.472719818353653</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>6.499740543918538</v>
+        <v>4.989783916470055</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.4781464040279388</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>6.499740399934631</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4714722633361816</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>6.499740240794523</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4702708125114441</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>6.499740293841225</v>
+        <v>4.989783666392743</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.4151737093925476</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>6.499740240794523</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.4538704454898834</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.0740314606762854</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>6.499740240794523</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.5017460584640503</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.9867280899030685</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>6.499740058920113</v>
+        <v>4.989783431471631</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.5137689113616943</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9867280899030685</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>6.499740225638321</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.4622136950492859</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.2740314606762855</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>6.499740422668932</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4186707735061646</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4386651685504979</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>6.499740263528824</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4923827052116394</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.07403146067628553</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>6.499740301419325</v>
+        <v>4.989783673970843</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.5338965058326721</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.07403146067628551</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>6.499740498449936</v>
+        <v>4.989783871001453</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.4789094030857086</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2740314606762855</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>6.499740475715634</v>
+        <v>4.989783848267152</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.4353380799293518</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>6.499740324153627</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.4413755834102631</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>6.499740248372623</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.4555221498012543</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.07403146067628553</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>6.499740346887928</v>
+        <v>4.989783719439446</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.5217356085777283</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.07403146067628553</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>6.499740354466028</v>
+        <v>4.989783727017546</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4955600202083588</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.2740314606762856</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>6.499740619699542</v>
+        <v>4.98978399225106</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4625402987003326</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.2740314606762856</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>6.499740324153627</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.5117690563201904</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.2740314606762856</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC92" t="n">
-        <v>6.499740566652839</v>
+        <v>4.989783939204357</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.4563672244548798</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9867280899030687</v>
+        <v>0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>6.499740650011944</v>
+        <v>4.989784022563462</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.6181225776672363</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9867280899030687</v>
+        <v>0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>6.499740483293736</v>
+        <v>4.989783855845253</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.533800482749939</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.9867280899030687</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>6.499740672746245</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4940802454948425</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.2740314606762856</v>
+        <v>0.16</v>
       </c>
       <c r="JC96" t="n">
-        <v>6.499740324153627</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.4299466907978058</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>6.499740119544916</v>
+        <v>4.989783492096433</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4160845279693604</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>6.499740233216421</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.4598005712032318</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>6.499740248372623</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4589413106441498</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>6.499740013451511</v>
+        <v>4.989783386003029</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.4168316125869751</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>6.499740074076313</v>
+        <v>4.989783446627831</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.4048778712749481</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.07403146067628569</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>6.499739945248606</v>
+        <v>4.989783317800124</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.535106360912323</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.07403146067628565</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>6.499740081654415</v>
+        <v>4.989783454205933</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4475921988487244</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.2740314606762857</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>6.499740255950723</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.4225432872772217</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4386651685504979</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>6.499740399934631</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4512930512428284</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4386651685504979</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>6.499740233216421</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.4553378522396088</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>6.499740225638321</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.411628246307373</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>6.499739937670507</v>
+        <v>4.989783310222024</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4094825088977814</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>6.499739952826707</v>
+        <v>4.989783325378225</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4033768475055695</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>6.499740180169719</v>
+        <v>4.989783552721237</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.4462854564189911</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>6.499740165013518</v>
+        <v>4.989783537565036</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.392608642578125</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>6.499740271106924</v>
+        <v>4.989783643658441</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3972898423671722</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>6.49973999829531</v>
+        <v>4.989783370846827</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.4128655195236206</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>6.499740096810615</v>
+        <v>4.989783469362132</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.412400871515274</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>6.499740248372623</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4080378711223602</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>6.499740263528824</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.4228577017784119</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>6.499740240794523</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4458748400211334</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>6.499740324153627</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3952246308326721</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>6.499740422668932</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.3929070830345154</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>6.499740255950723</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4026053249835968</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>6.499740240794523</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4162405133247375</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>6.499740210482121</v>
+        <v>4.989783583033638</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4186041653156281</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>6.49974019532592</v>
+        <v>4.989783567877438</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4024549424648285</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>6.499740233216421</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.428552657365799</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.3700000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>6.499740248372623</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4715628027915955</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.7200000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>6.499740240794523</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_5_000007.xlsx
+++ b/out/MLP_Base_repeat_5_000007.xlsx
@@ -54209,7 +54209,7 @@
         <v>0.7682574987411499</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>4.989784136234967</v>
@@ -55004,7 +55004,7 @@
         <v>0.6392170190811157</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
         <v>4.989784166547369</v>
@@ -55799,7 +55799,7 @@
         <v>0.5761538147926331</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC69" t="n">
         <v>4.989783977094859</v>
@@ -56594,7 +56594,7 @@
         <v>0.5453459620475769</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.16</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>4.989784030141562</v>
@@ -57389,7 +57389,7 @@
         <v>0.4717177748680115</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
         <v>4.989784083188264</v>
@@ -66134,7 +66134,7 @@
         <v>0.4186707735061646</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>4.989783636080341</v>
@@ -66929,7 +66929,7 @@
         <v>0.4923827052116394</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>4.989783673970843</v>
@@ -67724,7 +67724,7 @@
         <v>0.5338965058326721</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>4.989783871001453</v>
@@ -68519,7 +68519,7 @@
         <v>0.4789094030857086</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>4.989783848267152</v>
@@ -69314,7 +69314,7 @@
         <v>0.4353380799293518</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>4.989783696705144</v>
@@ -71699,7 +71699,7 @@
         <v>0.5217356085777283</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC89" t="n">
         <v>4.989783727017546</v>
@@ -72494,7 +72494,7 @@
         <v>0.4955600202083588</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC90" t="n">
         <v>4.98978399225106</v>
@@ -73289,7 +73289,7 @@
         <v>0.4625402987003326</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>4.989783696705144</v>
@@ -74084,7 +74084,7 @@
         <v>0.5117690563201904</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>4.989783939204357</v>
@@ -74879,7 +74879,7 @@
         <v>0.4563672244548798</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="JC93" t="n">
         <v>4.989784022563462</v>
@@ -75674,7 +75674,7 @@
         <v>0.6181225776672363</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.3</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC94" t="n">
         <v>4.989783855845253</v>
